--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.39489506903892</v>
+        <v>8.514170448718824</v>
       </c>
       <c r="D2" t="n">
-        <v>41.4392448088772</v>
+        <v>6.733877281442545</v>
       </c>
       <c r="E2" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F2" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.09694789795073</v>
+        <v>11.39075403341699</v>
       </c>
       <c r="D3" t="n">
-        <v>68.7232462185512</v>
+        <v>11.16752751051457</v>
       </c>
       <c r="E3" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F3" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.30870124428507</v>
+        <v>9.962663952196325</v>
       </c>
       <c r="D4" t="n">
-        <v>48.97902045207154</v>
+        <v>7.959090823461627</v>
       </c>
       <c r="E4" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F4" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.78458023073938</v>
+        <v>5.97749428749515</v>
       </c>
       <c r="D5" t="n">
-        <v>35.10330120241952</v>
+        <v>5.704286445393172</v>
       </c>
       <c r="E5" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F5" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.46912109584685</v>
+        <v>3.326232178075113</v>
       </c>
       <c r="D6" t="n">
-        <v>18.86796226411321</v>
+        <v>3.066043867918396</v>
       </c>
       <c r="E6" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F6" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.4709084800135</v>
+        <v>4.951522628002194</v>
       </c>
       <c r="D7" t="n">
-        <v>26.51886121235224</v>
+        <v>4.309314947007238</v>
       </c>
       <c r="E7" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F7" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.36256470200795</v>
+        <v>3.308916764076292</v>
       </c>
       <c r="D8" t="n">
-        <v>12.58967831201417</v>
+        <v>2.045822725702303</v>
       </c>
       <c r="E8" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F8" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.87180254150624</v>
+        <v>2.904167912994764</v>
       </c>
       <c r="D9" t="n">
-        <v>12.98943771450434</v>
+        <v>2.110783628606956</v>
       </c>
       <c r="E9" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F9" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>52.09905323454657</v>
+        <v>8.466096150613819</v>
       </c>
       <c r="D10" t="n">
-        <v>38.23063941557159</v>
+        <v>6.212478905030385</v>
       </c>
       <c r="E10" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F10" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.78525513623397</v>
+        <v>4.027603959638021</v>
       </c>
       <c r="D11" t="n">
-        <v>25.47334614445377</v>
+        <v>4.139418748473738</v>
       </c>
       <c r="E11" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F11" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.87551078930716</v>
+        <v>2.092270503262414</v>
       </c>
       <c r="D12" t="n">
-        <v>9.17877987534291</v>
+        <v>1.491551729743223</v>
       </c>
       <c r="E12" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F12" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.98066020165223</v>
+        <v>3.734357282768487</v>
       </c>
       <c r="D13" t="n">
-        <v>9.961920495320152</v>
+        <v>1.618812080489525</v>
       </c>
       <c r="E13" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F13" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>3.4676205271991</v>
+        <v>0.5634883356698538</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.08125</v>
       </c>
       <c r="E14" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F14" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.40001630322512</v>
+        <v>6.402502649274082</v>
       </c>
       <c r="D15" t="n">
-        <v>36.25878414481068</v>
+        <v>5.892052423531735</v>
       </c>
       <c r="E15" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F15" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>33.83648000293043</v>
+        <v>5.498428000476195</v>
       </c>
       <c r="D16" t="n">
-        <v>19.64235304646164</v>
+        <v>3.191882370050017</v>
       </c>
       <c r="E16" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F16" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>49.55730720621192</v>
+        <v>8.053062421009436</v>
       </c>
       <c r="D17" t="n">
-        <v>51.73732499388606</v>
+        <v>8.407315311506485</v>
       </c>
       <c r="E17" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F17" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>16.50220099667579</v>
+        <v>2.681607661959816</v>
       </c>
       <c r="D18" t="n">
-        <v>11.10180165558726</v>
+        <v>1.80404276903293</v>
       </c>
       <c r="E18" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F18" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25.06816651568514</v>
+        <v>4.073577058798835</v>
       </c>
       <c r="D19" t="n">
-        <v>20.59319219174811</v>
+        <v>3.346393731159067</v>
       </c>
       <c r="E19" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F19" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>27.37888992658177</v>
+        <v>4.449069613069537</v>
       </c>
       <c r="D20" t="n">
-        <v>16.72619577190223</v>
+        <v>2.718006812934112</v>
       </c>
       <c r="E20" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F20" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>21.73934114742581</v>
+        <v>3.532642936456694</v>
       </c>
       <c r="D21" t="n">
-        <v>15.57241150239744</v>
+        <v>2.530516869139583</v>
       </c>
       <c r="E21" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F21" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>35.5611215261489</v>
+        <v>5.778682247999195</v>
       </c>
       <c r="D22" t="n">
-        <v>47.87881509090726</v>
+        <v>7.78030745227243</v>
       </c>
       <c r="E22" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F22" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>21.04886542873716</v>
+        <v>3.420440632169788</v>
       </c>
       <c r="D23" t="n">
-        <v>19.06066517506931</v>
+        <v>3.097358090948763</v>
       </c>
       <c r="E23" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F23" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>16.81694374524369</v>
+        <v>2.732753358602101</v>
       </c>
       <c r="D24" t="n">
-        <v>11.75765576702272</v>
+        <v>1.910619062141192</v>
       </c>
       <c r="E24" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F24" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>25.01711435063606</v>
+        <v>4.06528108197836</v>
       </c>
       <c r="D25" t="n">
-        <v>16.3957386815471</v>
+        <v>2.664307535751405</v>
       </c>
       <c r="E25" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F25" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>30.66034372381593</v>
+        <v>4.982305855120089</v>
       </c>
       <c r="D26" t="n">
-        <v>30.01817692530431</v>
+        <v>4.877953750361951</v>
       </c>
       <c r="E26" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F26" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>13.17414189403475</v>
+        <v>2.140798057780647</v>
       </c>
       <c r="D27" t="n">
-        <v>12.345020047269</v>
+        <v>2.006065757681213</v>
       </c>
       <c r="E27" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F27" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>8.544744121698749</v>
+        <v>1.388520919776047</v>
       </c>
       <c r="D28" t="n">
-        <v>7.57730609465013</v>
+        <v>1.231312240380646</v>
       </c>
       <c r="E28" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F28" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>36.93038333949549</v>
+        <v>6.001187292668018</v>
       </c>
       <c r="D29" t="n">
-        <v>40.75634928096971</v>
+        <v>6.622906758157578</v>
       </c>
       <c r="E29" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F29" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>17.26108887050006</v>
+        <v>2.804926941456261</v>
       </c>
       <c r="D30" t="n">
-        <v>64.22753418711832</v>
+        <v>10.43697430540673</v>
       </c>
       <c r="E30" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F30" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>21.90573736968167</v>
+        <v>3.559682322573272</v>
       </c>
       <c r="D31" t="n">
-        <v>7.890187339128408</v>
+        <v>1.282155442608366</v>
       </c>
       <c r="E31" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F31" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>37.53927474684178</v>
+        <v>6.100132146361789</v>
       </c>
       <c r="D32" t="n">
-        <v>37.14432238929098</v>
+        <v>6.035952388259784</v>
       </c>
       <c r="E32" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F32" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>5.303511400906759</v>
+        <v>0.8618206026473483</v>
       </c>
       <c r="D33" t="n">
-        <v>6.173977464322972</v>
+        <v>1.003271337952483</v>
       </c>
       <c r="E33" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F33" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>14.98632734805105</v>
+        <v>2.435278194058296</v>
       </c>
       <c r="D34" t="n">
-        <v>14.86745289693498</v>
+        <v>2.415961095751934</v>
       </c>
       <c r="E34" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F34" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>30.23818115449547</v>
+        <v>4.913704437605515</v>
       </c>
       <c r="D35" t="n">
-        <v>30.13740653576819</v>
+        <v>4.89732856206233</v>
       </c>
       <c r="E35" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F35" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>27.8151984084021</v>
+        <v>4.519969741365341</v>
       </c>
       <c r="D36" t="n">
-        <v>21.51815872514665</v>
+        <v>3.496700792836331</v>
       </c>
       <c r="E36" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F36" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>6.339969719910559</v>
+        <v>1.030245079485466</v>
       </c>
       <c r="D37" t="n">
-        <v>42.00757529274235</v>
+        <v>6.826230985070631</v>
       </c>
       <c r="E37" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F37" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>30.38769281411137</v>
+        <v>4.938000082293098</v>
       </c>
       <c r="D38" t="n">
-        <v>30.67562615192916</v>
+        <v>4.984789249688489</v>
       </c>
       <c r="E38" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F38" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>22.15362277356132</v>
+        <v>3.599963700703715</v>
       </c>
       <c r="D39" t="n">
-        <v>22.79347907272843</v>
+        <v>3.703940349318371</v>
       </c>
       <c r="E39" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F39" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>39.94588238524524</v>
+        <v>6.491205887602352</v>
       </c>
       <c r="D40" t="n">
-        <v>40.0844404207721</v>
+        <v>6.513721568375466</v>
       </c>
       <c r="E40" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F40" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>28.75244570559065</v>
+        <v>4.672272427158481</v>
       </c>
       <c r="D41" t="n">
-        <v>29.68290389063784</v>
+        <v>4.823471882228649</v>
       </c>
       <c r="E41" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F41" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>28.44917884783692</v>
+        <v>4.6229915627735</v>
       </c>
       <c r="D42" t="n">
-        <v>29.18899344189762</v>
+        <v>4.743211434308364</v>
       </c>
       <c r="E42" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F42" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>43.36596368911637</v>
+        <v>7.04696909948141</v>
       </c>
       <c r="D43" t="n">
-        <v>43.92860927276937</v>
+        <v>7.138399006825023</v>
       </c>
       <c r="E43" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F43" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>38.94525910899485</v>
+        <v>6.328604605211662</v>
       </c>
       <c r="D44" t="n">
-        <v>39.67212098462581</v>
+        <v>6.446719660001695</v>
       </c>
       <c r="E44" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F44" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>27.61053188056691</v>
+        <v>4.486711430592123</v>
       </c>
       <c r="D45" t="n">
-        <v>28.58250284503937</v>
+        <v>4.644656712318898</v>
       </c>
       <c r="E45" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F45" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>20.22221767809801</v>
+        <v>3.286110372690926</v>
       </c>
       <c r="D46" t="n">
-        <v>21.88810590147915</v>
+        <v>3.556817208990362</v>
       </c>
       <c r="E46" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F46" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>13.20643017159621</v>
+        <v>2.146044902884384</v>
       </c>
       <c r="D47" t="n">
-        <v>15.25272556168499</v>
+        <v>2.47856790377381</v>
       </c>
       <c r="E47" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F47" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>39.09501533191548</v>
+        <v>6.352939991436265</v>
       </c>
       <c r="D48" t="n">
-        <v>40.07641033199646</v>
+        <v>6.512416678949425</v>
       </c>
       <c r="E48" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F48" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>44.08204759215842</v>
+        <v>7.163332733725743</v>
       </c>
       <c r="D49" t="n">
-        <v>44.43840429994582</v>
+        <v>7.221240698741195</v>
       </c>
       <c r="E49" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F49" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>13.37807346156965</v>
+        <v>2.173936937505068</v>
       </c>
       <c r="D50" t="n">
-        <v>14.27824745467169</v>
+        <v>2.32021521138415</v>
       </c>
       <c r="E50" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F50" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>46.31014435313708</v>
+        <v>7.525398457384775</v>
       </c>
       <c r="D51" t="n">
-        <v>46.45337016826277</v>
+        <v>7.5486726523427</v>
       </c>
       <c r="E51" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F51" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>6.796171018441275</v>
+        <v>1.104377790496707</v>
       </c>
       <c r="D52" t="n">
-        <v>7.508927988664192</v>
+        <v>1.220200798157931</v>
       </c>
       <c r="E52" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F52" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>60.43976589602856</v>
+        <v>9.821461958104642</v>
       </c>
       <c r="D53" t="n">
-        <v>61.42327777229163</v>
+        <v>9.98128263799739</v>
       </c>
       <c r="E53" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F53" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>5.662611701630237</v>
+        <v>0.9201744015149135</v>
       </c>
       <c r="D54" t="n">
-        <v>4.223677936912614</v>
+        <v>0.6863476647482998</v>
       </c>
       <c r="E54" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F54" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>61.46380967683989</v>
+        <v>9.987869072486482</v>
       </c>
       <c r="D55" t="n">
-        <v>62.44227174600515</v>
+        <v>10.14686915872584</v>
       </c>
       <c r="E55" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F55" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>43.99722891992116</v>
+        <v>7.149549699487189</v>
       </c>
       <c r="D56" t="n">
-        <v>43.74590909149178</v>
+        <v>7.108710227367414</v>
       </c>
       <c r="E56" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F56" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>35.52146745904521</v>
+        <v>5.772238462094847</v>
       </c>
       <c r="D57" t="n">
-        <v>34.81402318710134</v>
+        <v>5.657278767903968</v>
       </c>
       <c r="E57" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F57" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>62.06816467108408</v>
+        <v>10.08607675905116</v>
       </c>
       <c r="D58" t="n">
-        <v>61.62309474849336</v>
+        <v>10.01375289663017</v>
       </c>
       <c r="E58" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F58" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>72.06387608964803</v>
+        <v>11.71037986456781</v>
       </c>
       <c r="D59" t="n">
-        <v>73.07253117747476</v>
+        <v>11.87428631633965</v>
       </c>
       <c r="E59" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F59" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>21.74097930893839</v>
+        <v>3.532909137702488</v>
       </c>
       <c r="D60" t="n">
-        <v>19.83113250539907</v>
+        <v>3.222559032127348</v>
       </c>
       <c r="E60" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F60" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>76.59468631034702</v>
+        <v>12.44663652543139</v>
       </c>
       <c r="D61" t="n">
-        <v>77.4772166391038</v>
+        <v>12.59004770385437</v>
       </c>
       <c r="E61" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F61" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>76.91458193861385</v>
+        <v>12.49861956502475</v>
       </c>
       <c r="D62" t="n">
-        <v>77.84472161944849</v>
+        <v>12.64976726316038</v>
       </c>
       <c r="E62" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F62" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>73.60456563642487</v>
+        <v>11.96074191591904</v>
       </c>
       <c r="D63" t="n">
-        <v>74.59863444610112</v>
+        <v>12.12227809749143</v>
       </c>
       <c r="E63" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F63" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>37.57577795366192</v>
+        <v>6.106063917470062</v>
       </c>
       <c r="D64" t="n">
-        <v>36.35291386093174</v>
+        <v>5.907348502401408</v>
       </c>
       <c r="E64" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F64" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>25.46702178913412</v>
+        <v>4.138391040734295</v>
       </c>
       <c r="D65" t="n">
-        <v>23.49941985546445</v>
+        <v>3.818655726512973</v>
       </c>
       <c r="E65" t="n">
-        <v>18.65834480346211</v>
+        <v>3.031981030562592</v>
       </c>
       <c r="F65" t="n">
-        <v>19.74150223939161</v>
+        <v>3.207994113901136</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
